--- a/cet4/result/76_职场女神_工程师的逆袭之路/76_职场女神_工程师的逆袭之路_学习版.xlsx
+++ b/cet4/result/76_职场女神_工程师的逆袭之路/76_职场女神_工程师的逆袭之路_学习版.xlsx
@@ -397,829 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>autumn</v>
       </c>
       <c r="B2" t="str">
-        <v>autumn</v>
+        <v>/ˈɔːtəm/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>秋天</v>
       </c>
-      <c r="D2" t="str">
-        <v>autumn(秋天)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>establishment</v>
       </c>
       <c r="B3" t="str">
-        <v>establishment</v>
+        <v>/ɪˈstæblɪʃmənt/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>公司</v>
       </c>
-      <c r="D3" t="str">
-        <v>establishment(公司)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>engineering</v>
       </c>
       <c r="B4" t="str">
-        <v>engineering</v>
+        <v>/ˌendʒɪˈnɪrɪŋ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D4" t="str">
         <v>工程</v>
       </c>
-      <c r="D4" t="str">
-        <v>engineering(工程)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>complex</v>
       </c>
       <c r="B5" t="str">
-        <v>complex</v>
+        <v>/kəmˈpleks,ˈkɑːmpleks/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>复杂的</v>
       </c>
-      <c r="D5" t="str">
-        <v>complex(复杂的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>exclude</v>
       </c>
       <c r="B6" t="str">
-        <v>exclude</v>
+        <v>/ɪkˈskluːd/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D6" t="str">
         <v>排除</v>
       </c>
-      <c r="D6" t="str">
-        <v>exclude(排除)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>virtually</v>
       </c>
       <c r="B7" t="str">
-        <v>virtually</v>
+        <v>/ˈvɜːrtʃuəli/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>几乎</v>
       </c>
-      <c r="D7" t="str">
-        <v>virtually(几乎)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>setting</v>
       </c>
       <c r="B8" t="str">
-        <v>setting</v>
+        <v>/ˈsetɪŋ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>环境</v>
       </c>
-      <c r="D8" t="str">
-        <v>setting(环境)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>several</v>
       </c>
       <c r="B9" t="str">
-        <v>several</v>
+        <v>/ˈsevrəl/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj./pron.</v>
+      </c>
+      <c r="D9" t="str">
         <v>几个</v>
       </c>
-      <c r="D9" t="str">
-        <v>several(几个)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>job</v>
       </c>
       <c r="B10" t="str">
-        <v>job</v>
+        <v>/dʒɑːb/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>工作</v>
       </c>
-      <c r="D10" t="str">
-        <v>job(工作)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>locomotive</v>
       </c>
       <c r="B11" t="str">
-        <v>locomotive</v>
+        <v>/ˌloʊkəˈmoʊtɪv/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>机车</v>
       </c>
-      <c r="D11" t="str">
-        <v>locomotive(机车)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>upper</v>
       </c>
       <c r="B12" t="str">
-        <v>upper</v>
+        <v>/ˈʌpər/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>上面的</v>
       </c>
-      <c r="D12" t="str">
-        <v>upper(上面的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>fellow</v>
       </c>
       <c r="B13" t="str">
-        <v>fellow</v>
+        <v>/ˈfeloʊ/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>同事</v>
       </c>
-      <c r="D13" t="str">
-        <v>fellow(同事)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>faith</v>
       </c>
       <c r="B14" t="str">
-        <v>faith</v>
+        <v>/feɪθ/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>信仰</v>
       </c>
-      <c r="D14" t="str">
-        <v>faith(信仰)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>detect</v>
       </c>
       <c r="B15" t="str">
-        <v>detect</v>
+        <v>/dɪˈtekt/</v>
       </c>
       <c r="C15" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D15" t="str">
         <v>发现</v>
       </c>
-      <c r="D15" t="str">
-        <v>detect(发现)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>tramp</v>
       </c>
       <c r="B16" t="str">
-        <v>tramp</v>
+        <v>/træmp/</v>
       </c>
       <c r="C16" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D16" t="str">
         <v>践踏</v>
       </c>
-      <c r="D16" t="str">
-        <v>tramp(践踏)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>housewife</v>
       </c>
       <c r="B17" t="str">
-        <v>housewife</v>
+        <v>/ˈhaʊswaɪf/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>家庭主妇</v>
       </c>
-      <c r="D17" t="str">
-        <v>housewife(家庭主妇)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>enjoy</v>
       </c>
       <c r="B18" t="str">
-        <v>enjoy</v>
+        <v>/ɪnˈdʒɔɪ/</v>
       </c>
       <c r="C18" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>享受</v>
       </c>
-      <c r="D18" t="str">
-        <v>enjoy(享受)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>conflict</v>
       </c>
       <c r="B19" t="str">
-        <v>conflict</v>
+        <v>/ˈkɑːnflɪkt/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>冲突</v>
       </c>
-      <c r="D19" t="str">
-        <v>conflict(冲突)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>stewardess</v>
       </c>
       <c r="B20" t="str">
-        <v>stewardess</v>
+        <v>/ˈstuːərdəs/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>女服务员</v>
       </c>
-      <c r="D20" t="str">
-        <v>stewardess(女服务员)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>sin</v>
       </c>
       <c r="B21" t="str">
-        <v>sin</v>
+        <v>/sɪn/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D21" t="str">
         <v>罪恶</v>
       </c>
-      <c r="D21" t="str">
-        <v>sin(罪恶)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>consequently</v>
       </c>
       <c r="B22" t="str">
-        <v>consequently</v>
+        <v>/ˈkɑːnsɪkwentli/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D22" t="str">
         <v>因此</v>
       </c>
-      <c r="D22" t="str">
-        <v>consequently(因此)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>meaning</v>
       </c>
       <c r="B23" t="str">
-        <v>meaning</v>
+        <v>/ˈmiːnɪŋ/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>意义</v>
       </c>
-      <c r="D23" t="str">
-        <v>meaning(意义)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>elect</v>
       </c>
       <c r="B24" t="str">
-        <v>elect</v>
+        <v>/ɪˈlekt/</v>
       </c>
       <c r="C24" t="str">
+        <v>vt./v.</v>
+      </c>
+      <c r="D24" t="str">
         <v>推选</v>
       </c>
-      <c r="D24" t="str">
-        <v>elect(推选)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>quit</v>
       </c>
       <c r="B25" t="str">
-        <v>several</v>
+        <v>/kwɪt/</v>
       </c>
       <c r="C25" t="str">
-        <v>几个</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>several(几个)📢</v>
+        <v>放弃</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>pollution</v>
       </c>
       <c r="B26" t="str">
-        <v>quit</v>
+        <v>/pəˈluːʃn/</v>
       </c>
       <c r="C26" t="str">
-        <v>放弃</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>quit(放弃)📢</v>
+        <v>污染</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>arrow</v>
       </c>
       <c r="B27" t="str">
-        <v>pollution</v>
+        <v>/ˈæroʊ/</v>
       </c>
       <c r="C27" t="str">
-        <v>污染</v>
+        <v>n./vt.</v>
       </c>
       <c r="D27" t="str">
-        <v>pollution(污染)📢</v>
+        <v>箭头</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>forever</v>
       </c>
       <c r="B28" t="str">
-        <v>arrow</v>
+        <v>/fərˈevər/</v>
       </c>
       <c r="C28" t="str">
-        <v>箭头</v>
+        <v>v./adv.</v>
       </c>
       <c r="D28" t="str">
-        <v>arrow(箭头)📢</v>
+        <v>永远</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>search</v>
       </c>
       <c r="B29" t="str">
-        <v>forever</v>
+        <v>/sɜːrtʃ/</v>
       </c>
       <c r="C29" t="str">
-        <v>永远</v>
+        <v>n./v.</v>
       </c>
       <c r="D29" t="str">
-        <v>forever(永远)📢</v>
+        <v>搜索</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>rat</v>
       </c>
       <c r="B30" t="str">
-        <v>search</v>
+        <v>/ræt/</v>
       </c>
       <c r="C30" t="str">
-        <v>搜索</v>
+        <v>n./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>search(搜索)📢</v>
+        <v>老鼠</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>reply</v>
       </c>
       <c r="B31" t="str">
-        <v>rat</v>
+        <v>/rɪˈplaɪ/</v>
       </c>
       <c r="C31" t="str">
-        <v>老鼠</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>rat(老鼠)📢</v>
+        <v>报告</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>sponge</v>
       </c>
       <c r="B32" t="str">
-        <v>reply</v>
+        <v>/spʌndʒ/</v>
       </c>
       <c r="C32" t="str">
-        <v>报告</v>
+        <v>n./v.</v>
       </c>
       <c r="D32" t="str">
-        <v>reply(报告)📢</v>
+        <v>海绵</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>temporary</v>
       </c>
       <c r="B33" t="str">
-        <v>sponge</v>
+        <v>/ˈtempəreri/</v>
       </c>
       <c r="C33" t="str">
-        <v>海绵</v>
+        <v>n./adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>sponge(海绵)📢</v>
+        <v>临时的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>income</v>
       </c>
       <c r="B34" t="str">
-        <v>several</v>
+        <v>/ˈɪnkʌm,ˈɪnkəm/</v>
       </c>
       <c r="C34" t="str">
-        <v>几个</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>several(几个)📢</v>
+        <v>收入</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>sell</v>
       </c>
       <c r="B35" t="str">
-        <v>temporary</v>
+        <v>/sel/</v>
       </c>
       <c r="C35" t="str">
-        <v>临时的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>temporary(临时的)📢</v>
+        <v>出售</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>opening</v>
       </c>
       <c r="B36" t="str">
-        <v>income</v>
+        <v>/ˈoʊpənɪŋ/</v>
       </c>
       <c r="C36" t="str">
-        <v>收入</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D36" t="str">
-        <v>income(收入)📢</v>
+        <v>机会</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>shift</v>
       </c>
       <c r="B37" t="str">
-        <v>sell</v>
+        <v>/ʃɪft/</v>
       </c>
       <c r="C37" t="str">
-        <v>出售</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>sell(出售)📢</v>
+        <v>转变</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>misunderstand</v>
       </c>
       <c r="B38" t="str">
-        <v>establishment</v>
+        <v>/ˌmɪsʌndərˈstænd/</v>
       </c>
       <c r="C38" t="str">
-        <v>公司</v>
+        <v>vt.</v>
       </c>
       <c r="D38" t="str">
-        <v>establishment(公司)📢</v>
+        <v>误解</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>code</v>
       </c>
       <c r="B39" t="str">
-        <v>opening</v>
+        <v>/koʊd/</v>
       </c>
       <c r="C39" t="str">
-        <v>机会</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>opening(机会)📢</v>
+        <v>代码</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>sightseeing</v>
       </c>
       <c r="B40" t="str">
-        <v>shift</v>
+        <v>/ˈsaɪtsiːɪŋ/</v>
       </c>
       <c r="C40" t="str">
-        <v>转变</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>shift(转变)📢</v>
+        <v>游览</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>lamb</v>
       </c>
       <c r="B41" t="str">
-        <v>misunderstand</v>
+        <v>/læm/</v>
       </c>
       <c r="C41" t="str">
-        <v>误解</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>misunderstand(误解)📢</v>
+        <v>羔羊</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>swan</v>
       </c>
       <c r="B42" t="str">
-        <v>code</v>
+        <v>/swɑːn/</v>
       </c>
       <c r="C42" t="str">
-        <v>代码</v>
+        <v>n./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>code(代码)📢</v>
+        <v>天鹅</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>landing</v>
       </c>
       <c r="B43" t="str">
-        <v>autumn</v>
+        <v>/ˈlændɪŋ/</v>
       </c>
       <c r="C43" t="str">
-        <v>秋天</v>
+        <v>n./v.</v>
       </c>
       <c r="D43" t="str">
-        <v>autumn(秋天)📢</v>
+        <v>楼梯平台</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>elephant</v>
       </c>
       <c r="B44" t="str">
-        <v>sightseeing</v>
+        <v>/ˈelɪfənt/</v>
       </c>
       <c r="C44" t="str">
-        <v>游览</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>sightseeing(游览)📢</v>
+        <v>象</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>pray</v>
       </c>
       <c r="B45" t="str">
-        <v>lamb</v>
+        <v>/preɪ/</v>
       </c>
       <c r="C45" t="str">
-        <v>羔羊</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>lamb(羔羊)📢</v>
+        <v>祈祷</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>sprinkle</v>
       </c>
       <c r="B46" t="str">
-        <v>swan</v>
+        <v>/ˈsprɪŋkl/</v>
       </c>
       <c r="C46" t="str">
-        <v>天鹅</v>
+        <v>n./v.</v>
       </c>
       <c r="D46" t="str">
-        <v>swan(天鹅)📢</v>
+        <v>撒</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>heir</v>
       </c>
       <c r="B47" t="str">
-        <v>landing</v>
+        <v>/er/</v>
       </c>
       <c r="C47" t="str">
-        <v>楼梯平台</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>landing(楼梯平台)📢</v>
+        <v>继承人</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>regarding</v>
       </c>
       <c r="B48" t="str">
-        <v>elephant</v>
+        <v>/rɪˈɡɑːrdɪŋ/</v>
       </c>
       <c r="C48" t="str">
-        <v>象</v>
+        <v>v./prep.</v>
       </c>
       <c r="D48" t="str">
-        <v>elephant(象)📢</v>
+        <v>关于</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>silk</v>
       </c>
       <c r="B49" t="str">
-        <v>pray</v>
+        <v>/sɪlk/</v>
       </c>
       <c r="C49" t="str">
-        <v>祈祷</v>
+        <v>n./vi./adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>pray(祈祷)📢</v>
+        <v>丝绸</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>bicycle</v>
       </c>
       <c r="B50" t="str">
-        <v>sprinkle</v>
+        <v>/ˈbaɪsɪkl/</v>
       </c>
       <c r="C50" t="str">
-        <v>撒</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>sprinkle(撒)📢</v>
+        <v>自行车</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>lick</v>
       </c>
       <c r="B51" t="str">
-        <v>heir</v>
+        <v>/lɪk/</v>
       </c>
       <c r="C51" t="str">
-        <v>继承人</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D51" t="str">
-        <v>heir(继承人)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>regarding</v>
-      </c>
-      <c r="C52" t="str">
-        <v>关于</v>
-      </c>
-      <c r="D52" t="str">
-        <v>regarding(关于)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>silk</v>
-      </c>
-      <c r="C53" t="str">
-        <v>丝绸</v>
-      </c>
-      <c r="D53" t="str">
-        <v>silk(丝绸)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>autumn</v>
-      </c>
-      <c r="C54" t="str">
-        <v>秋天</v>
-      </c>
-      <c r="D54" t="str">
-        <v>autumn(秋天)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>bicycle</v>
-      </c>
-      <c r="C55" t="str">
-        <v>自行车</v>
-      </c>
-      <c r="D55" t="str">
-        <v>bicycle(自行车)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>lick</v>
-      </c>
-      <c r="C56" t="str">
         <v>舔</v>
-      </c>
-      <c r="D56" t="str">
-        <v>lick(舔)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>forever</v>
-      </c>
-      <c r="C57" t="str">
-        <v>永远</v>
-      </c>
-      <c r="D57" t="str">
-        <v>forever(永远)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>autumn</v>
-      </c>
-      <c r="C58" t="str">
-        <v>秋天</v>
-      </c>
-      <c r="D58" t="str">
-        <v>autumn(秋天)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>